--- a/nasdaq.xlsx
+++ b/nasdaq.xlsx
@@ -425,219 +425,69 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="n">
-        <v>10</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>世界の株価と日経平均先物</t>
+          <t>9H
+1D
+2D
+7D
+DOW CFD
+DOW
+NASDAQ
+SP500
+FTSE
+NK CFD
+VIX
+TNX
+USDJPY
+＄
+09:00
+12:00
+15:00
+18:00
+21:00
+【03/21】
+03:00
+06:00
+157.50
+158.00
+158.50
+159.00
+159.50
+51,600
+52,200
+52,800
+53,400
+54,000
+45,750
+45,250
+45,500
+46,000
+46,250
+46,500
+21,600
+21,750
+21,900
+22,050
+22,200
+https://nikkei225jp.com/nasdaq/
+9840
+9900
+9960
+10020
+10080
+10140</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>日経平均比較チャート</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>テクニカルチャート</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ADR株価</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>外部リンク
-経済指標予定 [外為どっとコム]
-スケジュール [TradersWeb]
-強弱材料・留意事項 [FISCO]
-要人発言 [TradersWeb]
-決算スケジュール [IFIS]
-IPOスケジュール [Tokyo IPO]
-市場休日 [Investing]
-市場休日 [みんかぶ]
-世界時計
-Yahoo!ファイナンス
-finance.yahoo.com</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>世界の株価
-日経先物CMENEW
-日経平均
-アジア株価
-ヨーロッパ株価
-NYダウ
-金 原油価格 UP
-為替
-ビットコイン</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>経済ニュース
-経済スケジュール
-日経平均寄与度
-業種別株価指数
-債券 国債利回り</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>日経平均PER
-騰落レシオ
-空売り比率
-投資主体別
-信用評価損益率
-裁定買い残 NEW
-恐怖指数
-ドル建て日経平均
-NT倍率
-新高値
-5分足カレンダー UP</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>MACD
-スローストキャスティクス
-ファストストキャスティクス
-モメンタム
-RSI
-移動平均乖離率
-RCI
-サイコロジカル
-ボリンジャーバンド
-一目均衡表</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ADR全銘柄
-ADR主要銘柄
-ADR個別詳細</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>世界の株価
-日経先物CMENEW
-日経平均
-アジア株価
-ヨーロッパ株価
-NYダウ
-金 原油価格 UP
-為替
-ビットコイン</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>経済ニュース
-経済スケジュール
-日経平均寄与度
-業種別株価指数
-債券 国債利回り</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>日経平均PER
-騰落レシオ
-空売り比率
-投資主体別
-信用評価損益率
-裁定買い残 NEW
-恐怖指数
-ドル建て日経平均
-NT倍率
-新高値
-5分足カレンダー UP</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>MACD
-スローストキャスティクス
-ファストストキャスティクス
-モメンタム
-RSI
-移動平均乖離率
-RCI
-サイコロジカル
-ボリンジャーバンド
-一目均衡表</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ADR全銘柄
-ADR主要銘柄
-ADR個別詳細</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/nasdaq.xlsx
+++ b/nasdaq.xlsx
@@ -429,63 +429,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9H
-1D
-2D
-7D
-DOW CFD
-DOW
-NASDAQ
-SP500
-FTSE
-NK CFD
-VIX
-TNX
-USDJPY
-＄
-09:00
-12:00
-15:00
-18:00
-21:00
-【03/21】
-03:00
-06:00
-157.50
-158.00
-158.50
-159.00
-159.50
-51,600
-52,200
-52,800
-53,400
-54,000
-45,750
-45,250
-45,500
-46,000
-46,250
-46,500
-21,600
-21,750
-21,900
-22,050
-22,200
-https://nikkei225jp.com/nasdaq/
-9840
-9900
-9960
-10020
-10080
-10140</t>
+          <t>6,506.48</t>
         </is>
       </c>
     </row>
